--- a/Excel/캐릭터_정보.xlsx
+++ b/Excel/캐릭터_정보.xlsx
@@ -28,17 +28,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="27">
+  <si>
+    <t>#Range=C2:F6</t>
+  </si>
   <si>
     <t>#Range=C2:G6</t>
   </si>
   <si>
-    <t>#Range=C2:F6</t>
-  </si>
-  <si>
-    <t>Id:pk</t>
-  </si>
-  <si>
     <t>id:pk</t>
   </si>
   <si>
@@ -84,25 +81,25 @@
     <t>5</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>플레이어블1</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>20</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>1,2</t>
   </si>
   <si>
+    <t>30</t>
+  </si>
+  <si>
     <t>플레이어블2</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>30</t>
   </si>
   <si>
     <t>15</t>
@@ -378,56 +375,56 @@
   <sheetData>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="C4" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>18</v>
@@ -435,36 +432,36 @@
     </row>
     <row r="5">
       <c r="C5" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>21</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="C6" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -482,78 +479,78 @@
   <sheetData>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="C4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="C5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="C6" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="F6" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
